--- a/Outputs/Scenarios/PtX_demand_RO_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_RO_Electrification.xlsx
@@ -501,7 +501,7 @@
         <v>0.01083623726744989</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003837294723497145</v>
+        <v>0.003837294723497144</v>
       </c>
       <c r="F2" t="n">
         <v>0.01645711450450432</v>
@@ -513,7 +513,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006753682897037698</v>
+        <v>0.0067536828970377</v>
       </c>
       <c r="J2" t="n">
         <v>0.0022912613703411</v>
@@ -550,7 +550,7 @@
         <v>1.5099343443556e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004504922364282553</v>
+        <v>0.0004504922364282554</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>6.918841025270782e-05</v>
+        <v>6.918841025270784e-05</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -735,7 +735,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003155790193653425</v>
+        <v>0.0003155790193653426</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -809,7 +809,7 @@
         <v>0.003749381908909639</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01508335591487949</v>
+        <v>0.0150833559148795</v>
       </c>
       <c r="J10" t="n">
         <v>0.0002528386855318</v>
@@ -846,7 +846,7 @@
         <v>0.0341995366953689</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09419884985513929</v>
+        <v>0.09419884985513931</v>
       </c>
       <c r="J11" t="n">
         <v>0.0015304330954511</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.002786133882873014</v>
+        <v>0.002786133882873013</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>0.0001935980702133385</v>
       </c>
       <c r="K42" t="n">
-        <v>0.002786133882873014</v>
+        <v>0.002786133882873013</v>
       </c>
     </row>
     <row r="43">

--- a/Outputs/Scenarios/PtX_demand_RO_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_RO_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.002484745587897071</v>
       </c>
       <c r="K16" t="n">
-        <v>0.002876372679448881</v>
+        <v>0.003651739830231575</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0004793954465748135</v>
+        <v>0.0005761261170361109</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.001917581786299254</v>
+        <v>0.002304504468144444</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.002876372679448881</v>
+        <v>0.002304504468144444</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>0.0001991279747961958</v>
       </c>
       <c r="K24" t="n">
-        <v>0.00422137136195661</v>
+        <v>0.004144362773768001</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.001205322050370813</v>
       </c>
       <c r="K25" t="n">
-        <v>0.03874865530372694</v>
+        <v>0.03804178092966951</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>3.580097795272014e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0004793954465748135</v>
+        <v>0.0005761261170361109</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.003678363334053432</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01671680329723808</v>
+        <v>0.0194556708633603</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.002786133882873013</v>
+        <v>0.003069473902835394</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.01114453553149205</v>
+        <v>0.01227789561134158</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.01671680329723808</v>
+        <v>0.01227789561134158</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0001935980702133385</v>
       </c>
       <c r="K42" t="n">
-        <v>0.002786133882873013</v>
+        <v>0.003069473902835394</v>
       </c>
     </row>
     <row r="43">
